--- a/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
@@ -10,6 +10,7 @@
     <sheet name="1. 테이블 목록" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2. 컬럼 정의" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3. 테이블 관계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. 명명·형식 규칙" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,7 +1030,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>물리명</t>
+          <t>영문명(예비)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -9118,4 +9119,159 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>컬럼명</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>한글 사용</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CSV 헤더는 한글을 정식 명칭으로 한다. '2. 컬럼 정의' 시트의 '영문명(예비)'은 BI 도구·DB가 한글 컬럼을 지원하지 않을 경우를 위한 대체안이며 현재 파일에는 쓰이지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>파일 형식</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CSV (UTF-8 BOM)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Excel에서 바로 열리도록 BOM을 포함한다. 구분자는 쉼표, 인용부호는 큰따옴표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>테이블명</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>영문 스네이크</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>dim_* 은 차원(변하지 않는 정의), fact_* 은 사실(측정값), micro_* 은 개인 단위 원자료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>결측 표현</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>빈칸</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>해당 지표 유형에 없는 통계량은 빈칸이다(예: 선택형 지표의 '지출자평균'). '대표값' 컬럼만 사용하면 지표 유형별 분기가 불필요하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>수치 자리수</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>원값 보존</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>평균 소수 4자리, 환산100·비율 2자리로 저장한다. 화면 표시용 반올림은 업체 측에서 처리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>코드값</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>코드+명칭 병기</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>지역규모·대분류·소주제 등은 코드 컬럼과 명칭 컬럼을 함께 제공한다. 정렬·필터는 코드, 표시는 명칭을 사용하면 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>갱신 방식</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>전체 교체</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>주기가 추가되면 전 파일을 재생성하여 교체한다. 증분 갱신은 지원하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
@@ -2941,17 +2941,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>학교키</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>school_key</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>SCH165</t>
         </is>
       </c>
     </row>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>응답자ID</t>
+          <t>응답자키</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>respondent_id</t>
+          <t>respondent_key</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>학생/학부모는 STUID, 교사는 TID. 주기 간 동일인 아님</t>
+          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>10011001</t>
+          <t>P21-008155</t>
         </is>
       </c>
     </row>
@@ -7513,17 +7513,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>학교키</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>school_key</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>SCH165</t>
         </is>
       </c>
     </row>
@@ -7985,17 +7985,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>응답자ID</t>
+          <t>응답자키</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>respondent_id</t>
+          <t>respondent_key</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>학생/학부모는 STUID, 교사는 TID. 주기 간 동일인 아님</t>
+          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>10011001</t>
+          <t>P21-008155</t>
         </is>
       </c>
     </row>
@@ -8025,17 +8025,17 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>학교키</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>school_key</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>SCH165</t>
         </is>
       </c>
     </row>
@@ -8497,17 +8497,17 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>응답자ID</t>
+          <t>응답자키</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>respondent_id</t>
+          <t>respondent_key</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>학생/학부모는 STUID, 교사는 TID. 주기 간 동일인 아님</t>
+          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>1001001</t>
+          <t>T21-004164</t>
         </is>
       </c>
     </row>
@@ -8537,17 +8537,17 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>학교키</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>school_key</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>SCH165</t>
         </is>
       </c>
     </row>

--- a/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -724,44 +724,44 @@
         <v>356</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>지역규모 결합 근거. 응답이 없는 학교도 포함되어 있음</t>
+          <t>지역규모 결합 근거. 응답 수집 여부를 응답주체별로 표기</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>사실</t>
+          <t>차원</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>지표별 집계 (전체·지역 통합)</t>
+          <t>응답주체 간 비교 성립 여부</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>02_집계/fact_indicator_wave.csv</t>
+          <t>01_정의/dim_cross_respondent.csv</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1371</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>★ 주력 테이블. 화면 ⑤-① 추이와 ⑤-② 지역 비교를 모두 커버</t>
+          <t>화면 ⑤ 다계열 그래프. 27개 조합 중 12개만 성립하므로 반드시 확인</t>
         </is>
       </c>
     </row>
@@ -773,28 +773,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>소주제별 집계</t>
+          <t>지표별 집계 (전체·지역 통합)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>02_집계/fact_topic_wave.csv</t>
+          <t>02_집계/fact_indicator_wave.csv</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>82</v>
+        <v>1371</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>화면 ④ 헤드라인 카드의 소주제 값</t>
+          <t>★ 주력 테이블. 화면 ⑤-① 추이와 ⑤-② 지역 비교를 모두 커버</t>
         </is>
       </c>
     </row>
@@ -806,28 +806,28 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>소주제 증감 순위</t>
+          <t>소주제별 집계</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>02_집계/fact_headline.csv</t>
+          <t>02_집계/fact_topic_wave.csv</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>화면 ④ 헤드라인 카드</t>
+          <t>화면 ④ 헤드라인 카드의 소주제 값</t>
         </is>
       </c>
     </row>
@@ -839,28 +839,28 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>선지별 응답 분포</t>
+          <t>소주제 증감 순위</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>02_집계/fact_indicator_dist.csv</t>
+          <t>02_집계/fact_headline.csv</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2068</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>화면 ⑤-③ 개별 문항 2시점 비교</t>
+          <t>화면 ④ 헤드라인 카드</t>
         </is>
       </c>
     </row>
@@ -872,59 +872,63 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>지표별 지역규모 집계 (분리본)</t>
+          <t>선지별 응답 분포</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>02_집계/fact_indicator_wave_region.csv</t>
+          <t>02_집계/fact_indicator_dist.csv</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>914</v>
+        <v>2068</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave의 지역 부분. 선택 사용</t>
+          <t>화면 ⑤-③ 개별 문항 2시점 비교</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>원자료</t>
+          <t>사실</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>학생 개인 단위 long</t>
+          <t>지표별 지역규모 집계 (분리본)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>03_마이크로데이터/micro_student.csv.gz</t>
+          <t>02_집계/fact_indicator_wave_region.csv</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1391643</v>
+        <v>914</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>fact_indicator_wave의 지역 부분. 선택 사용</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -934,21 +938,21 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>학부모 개인 단위 long</t>
+          <t>학생 개인 단위 long</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>03_마이크로데이터/micro_parent.csv.gz</t>
+          <t>03_마이크로데이터/micro_student.csv.gz</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>386360</v>
+        <v>1391643</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>13</v>
@@ -956,33 +960,62 @@
       <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>원자료</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>학부모 개인 단위 long</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>03_마이크로데이터/micro_parent.csv.gz</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>386360</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>원자료</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>micro_teacher</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>교사 개인 단위 long</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>03_마이크로데이터/micro_teacher.csv.gz</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>620342</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>집계 재현 및 연도 갱신용</t>
         </is>
@@ -999,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3197,20 +3230,20 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>학생응답</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>has_student</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3225,32 +3258,32 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>해당 주기에 이 학교에서 학생 응답이 수집되었는지 (Y/N)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>학부모응답</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>has_parent</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3265,37 +3298,37 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>해당 주기에 이 학교에서 학부모 응답이 수집되었는지 (Y/N)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>교사응답</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>has_teacher</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3305,32 +3338,32 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>해당 주기에 이 학교에서 교사 응답이 수집되었는지 (Y/N)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3343,39 +3376,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>'1주기' 또는 '2주기'</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>성립여부</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>is_valid</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3385,32 +3414,32 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>'성립'이면 다계열 그래프 구성 가능. '불가'는 한쪽 주체 문항이 미선택되어 단일 계열로 표시</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>성립</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>사유</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>invalid_reason</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3420,37 +3449,37 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>성립 불가 사유. 어느 주체가 미선택인지 표기</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>깨짐(학부모 미선택)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>비교조합</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3463,34 +3492,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>학생–학부모</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>주제</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>topic</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3503,36 +3528,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>대분류 표시명</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>전반적 학교만족도</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>topic_code</t>
-        </is>
-      </c>
+          <t>학생_1주기</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3543,36 +3560,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>Q28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>topic_name</t>
-        </is>
-      </c>
+          <t>학생_2주기</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3583,36 +3592,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>소주제 표시명</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>STQ32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>respondent</t>
-        </is>
-      </c>
+          <t>학생판정</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3623,36 +3624,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>① 연계가능</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>indicator_id</t>
-        </is>
-      </c>
+          <t>학부모_1주기</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3663,36 +3656,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>ST_COMP_AC_CONV</t>
+          <t>Q15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>indicator_name</t>
-        </is>
-      </c>
+          <t>학부모_2주기</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3703,36 +3688,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>자율적 역량 환산점수(0~100)</t>
+          <t>PRQ14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>stat_type</t>
-        </is>
-      </c>
+          <t>학부모판정</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3743,36 +3720,28 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>① 연계가능</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>comparable</t>
-        </is>
-      </c>
+          <t>교사_1주기</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3783,76 +3752,60 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>대표값</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>headline_value</t>
-        </is>
-      </c>
+          <t>교사_2주기</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>대표값유형</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>headline_value_type</t>
-        </is>
-      </c>
+          <t>교사판정</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3860,42 +3813,38 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>지출자 중앙값(만원)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>척도</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3903,39 +3852,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>5점 만족도</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>결측수</t>
+          <t>주의사항</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>caution</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3943,14 +3888,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>결측 응답자 수</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>단일 문항이고 양 주기·양 주체 모두 불변. 대시보드 대표 지표로 가</t>
         </is>
       </c>
     </row>
@@ -3961,21 +3902,21 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>평균</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3985,12 +3926,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>원 척도 기준 평균</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>70.2438</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -4001,21 +3942,21 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>표준편차</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4025,12 +3966,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>표본표준편차</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>13.5737</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -4041,21 +3982,21 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4065,12 +4006,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -4081,21 +4022,21 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>백분위25</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4103,10 +4044,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>'1주기' 또는 '2주기'</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
@@ -4117,21 +4062,21 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>백분위75</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4139,10 +4084,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>79.16666666666666</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4153,36 +4102,36 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>환산100</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>scaled_100</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
@@ -4193,36 +4142,36 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>상위2선지비율</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>top2_pct</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
@@ -4233,36 +4182,36 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>긍정응답률</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
@@ -4273,32 +4222,36 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>절사평균</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>trimmed_mean</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>70.6434</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
@@ -4309,32 +4262,36 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>지출자수</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>n_payers</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>소주제 표시명</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>8884.0</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4302,36 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>지출참여율</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>payer_pct</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
@@ -4381,32 +4342,36 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>지출자평균</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>payer_mean</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>70.2438</t>
+          <t>ST_COMP_AC_CONV</t>
         </is>
       </c>
     </row>
@@ -4417,56 +4382,56 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>지출자중앙값</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>payer_median</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>자율적 역량 환산점수(0~100)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>통계유형</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>stat_type</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4481,32 +4446,32 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>continuous</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4521,72 +4486,72 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>조건부</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>대표값</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>headline_value</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>대표값유형</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>headline_value_type</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4596,42 +4561,42 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>학업</t>
+          <t>지출자 중앙값(만원)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -4641,37 +4606,37 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>S0201A</t>
+          <t>8884</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>결측수</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>n_missing</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -4681,37 +4646,37 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>결측 응답자 수</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>학습동기(외재적)</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4721,37 +4686,37 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>원 척도 기준 평균</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>70.2438</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>표준편차</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -4761,37 +4726,37 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>표본표준편차</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>13.5737</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>median</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4801,37 +4766,37 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>지표수</t>
+          <t>백분위25</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>n_indicators</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4842,27 +4807,27 @@
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>62.5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>평균환산100</t>
+          <t>백분위75</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>mean_scaled_100</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4878,348 +4843,336 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>79.16666666666666</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>평균응답수</t>
+          <t>환산100</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>mean_n_valid</t>
+          <t>scaled_100</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>5923.0</t>
+          <t>21.82</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>상위2선지비율</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>top2_pct</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>7.31</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>긍정응답률</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>76.52</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>절사평균</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>trimmed_mean</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>70.6434</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>지출자수</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>n_payers</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>대분류 표시명</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>진로·진학</t>
+          <t>8884.0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>지출참여율</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>payer_pct</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>S1002</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>지출자평균</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>payer_mean</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>소주제 표시명</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>진로·진학 준비</t>
+          <t>70.2438</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>지출자중앙값</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>payer_median</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>값_2021</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>value_w1</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5227,35 +5180,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>값_2025</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>value_w2</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5263,35 +5220,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>증감</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -5299,35 +5260,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>C02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>증감률</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>delta_pct</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -5335,30 +5300,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>대분류 표시명</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>학업</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>변화방향</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5371,35 +5340,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>증가</t>
+          <t>S0201A</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>절대증감순위</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>abs_delta_rank</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5407,30 +5380,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>소주제 표시명</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>학습동기(외재적)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5445,37 +5422,37 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5485,32 +5462,32 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5525,37 +5502,37 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>PR_ASPIRE_01</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>지표수</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>n_indicators</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5563,39 +5540,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>평균환산100</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>mean_scaled_100</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -5603,39 +5576,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>대분류 표시명</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>진로·진학</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>평균응답수</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>mean_n_valid</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -5643,34 +5612,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>S1001</t>
+          <t>5923.0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5685,32 +5650,32 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>교육포부</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5725,32 +5690,32 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5765,37 +5730,37 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>교육포부 - 교육포부</t>
+          <t>C10</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -5805,32 +5770,32 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>진로·진학</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5845,37 +5810,37 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>S1002</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -5885,37 +5850,37 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>응답 선지 코드값</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>진로·진학 준비</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -5925,32 +5890,32 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>비율</t>
+          <t>값_2021</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>value_w1</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -5966,68 +5931,68 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>59.89</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>선지라벨</t>
+          <t>값_2025</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>option_label</t>
+          <t>value_w2</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>고등학교 졸업</t>
+          <t>72.09</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>직전시점</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>prev_year</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6037,37 +6002,37 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>증감 계산의 기준이 된 이전 조사연도</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>최신시점</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>curr_year</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -6077,37 +6042,37 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>증감 계산의 기준이 된 최근 조사연도</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>증감</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -6115,39 +6080,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>12.2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>증감률</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>delta_pct</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -6155,39 +6116,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>'1주기' 또는 '2주기'</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>20.37</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>변화방향</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -6195,39 +6152,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>증가</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>절대증감순위</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>abs_delta_rank</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6235,34 +6188,30 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6277,32 +6226,32 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6317,32 +6266,32 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6357,32 +6306,32 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>PR_ASPIRE_01</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6397,32 +6346,32 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>C10</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6437,32 +6386,32 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>진로·진학</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6477,32 +6426,32 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>ST_COMP_AC_CONV</t>
+          <t>S1001</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6517,32 +6466,32 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>자율적 역량 환산점수(0~100)</t>
+          <t>교육포부</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>stat_type</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6557,32 +6506,32 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>comparable</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6597,72 +6546,72 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>교육포부 - 교육포부</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>대표값</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>headline_value</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>대표값유형</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>headline_value_type</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -6672,37 +6621,37 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>지출자 중앙값(만원)</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>code</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -6717,32 +6666,32 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>응답 선지 코드값</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>결측수</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -6757,32 +6706,32 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>결측 응답자 수</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>평균</t>
+          <t>비율</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -6795,54 +6744,46 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>원 척도 기준 평균</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>70.3051</t>
+          <t>2.56</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>표준편차</t>
+          <t>선지라벨</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>option_label</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>표본표준편차</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>13.536</t>
+          <t>고등학교 졸업</t>
         </is>
       </c>
     </row>
@@ -6853,21 +6794,21 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -6877,12 +6818,12 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -6893,21 +6834,21 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>백분위25</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -6915,10 +6856,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -6929,21 +6874,21 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>백분위75</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -6951,10 +6896,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>79.16666666666666</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -6965,36 +6914,36 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>환산100</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>scaled_100</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
@@ -7005,36 +6954,36 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>상위2선지비율</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>top2_pct</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7045,36 +6994,36 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>긍정응답률</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
@@ -7085,32 +7034,36 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>절사평균</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>trimmed_mean</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>70.6843</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
@@ -7121,32 +7074,36 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>지출자수</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>n_payers</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>대분류 표시명</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>6985.0</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
@@ -7157,32 +7114,36 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>지출참여율</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>payer_pct</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
@@ -7193,32 +7154,36 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>지출자평균</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>payer_mean</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>소주제 표시명</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>70.3051</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
@@ -7229,56 +7194,56 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>지출자중앙값</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>payer_median</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -7293,32 +7258,32 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>ST_COMP_AC_CONV</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7333,37 +7298,37 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>자율적 역량 환산점수(0~100)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>통계유형</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>stat_type</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -7373,32 +7338,32 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>continuous</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7413,72 +7378,72 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>조건부</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>대표값</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>headline_value</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>응답자키</t>
+          <t>대표값유형</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>respondent_key</t>
+          <t>headline_value_type</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -7488,42 +7453,42 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
+          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>P21-008155</t>
+          <t>지출자 중앙값(만원)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -7533,37 +7498,37 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>6985</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>결측수</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>n_missing</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -7573,37 +7538,37 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>결측 응답자 수</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>ST_PRIVED_TYPE_01</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>원변수명</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>source_var</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7611,35 +7576,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>원 척도 기준 평균</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Q10_1_1</t>
+          <t>70.3051</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>표준편차</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -7649,32 +7618,32 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>응답값 (코드 또는 실수)</t>
+          <t>표본표준편차</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.536</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>결측보정</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>missing_fix</t>
+          <t>median</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -7684,38 +7653,42 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr"/>
+          <t>중앙값</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>70.83333333333334</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>백분위25</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -7723,39 +7696,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>62.5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>백분위75</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -7763,354 +7732,334 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>79.16666666666666</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>환산100</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>scaled_100</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>22.0</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>상위2선지비율</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>top2_pct</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>7.53</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>긍정응답률</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>78.3</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>절사평균</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>trimmed_mean</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>'1주기' 또는 '2주기'</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>70.6843</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>지출자수</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>n_payers</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>6985.0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>응답자키</t>
+          <t>지출참여율</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>respondent_key</t>
+          <t>payer_pct</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>P21-008155</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>지출자평균</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>payer_mean</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>70.3051</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>지출자중앙값</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>payer_median</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_01</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>원변수명</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>source_var</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8123,35 +8072,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Q3_1</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -8161,73 +8114,77 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>응답값 (코드 또는 실수)</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>결측보정</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>missing_fix</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr"/>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -8237,32 +8194,32 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8277,32 +8234,32 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>응답자키</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>respondent_key</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -8317,32 +8274,32 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>P21-008155</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>학교키</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>school_key</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -8357,37 +8314,37 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>SCH165</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -8397,32 +8354,32 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>원변수명</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>source_var</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -8435,39 +8392,35 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>'1주기' 또는 '2주기'</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>Q10_1_1</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>값</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -8477,77 +8430,73 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>응답값 (코드 또는 실수)</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>교사</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>응답자키</t>
+          <t>결측보정</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>respondent_key</t>
+          <t>missing_fix</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>T21-004164</t>
-        </is>
-      </c>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -8557,32 +8506,32 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_student</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -8597,32 +8546,32 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>TR_EFFICACY_01</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>원변수명</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>source_var</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -8635,35 +8584,39 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Q9_1</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -8673,126 +8626,954 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>응답값 (코드 또는 실수)</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>결측보정</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>missing_fix</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr"/>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>주기</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>wave_name</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>'1주기' 또는 '2주기'</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>1주기</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>응답주체</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>respondent</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>학부모</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>응답자키</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>respondent_key</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>P21-008155</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>학교키</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>school_key</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>SCH165</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>PR_EDU_COST_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>원변수명</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>source_var</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Q3_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>실수</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>응답값 (코드 또는 실수)</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>결측보정</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>missing_fix</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>실수</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>지역규모코드</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>region_code</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>지역규모</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>중소도시</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
           <t>micro_teacher</t>
         </is>
       </c>
-      <c r="B199" s="2" t="n">
+      <c r="B209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>조사명</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>survey_name</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>경기학교교육실태조사</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>학교급</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>school_level</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>중학교</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>조사연도</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>survey_year</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>주기</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>wave_name</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>'1주기' 또는 '2주기'</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>1주기</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>응답주체</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>respondent</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>교사</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>응답자키</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>respondent_key</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>T21-004164</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>학교키</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>school_key</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>SCH165</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>TR_EFFICACY_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>원변수명</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>source_var</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>Q9_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>응답값 (코드 또는 실수)</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>결측보정</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>missing_fix</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>실수</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>지역규모코드</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>region_code</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>정수</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
         <is>
           <t>micro_teacher</t>
         </is>
       </c>
-      <c r="B200" s="3" t="n">
+      <c r="B221" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t>지역규모</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>region_name</t>
         </is>
       </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>문자</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
         <is>
           <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
-      <c r="H200" s="3" t="inlineStr">
+      <c r="H221" s="3" t="inlineStr">
         <is>
           <t>중소도시</t>
         </is>

--- a/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
@@ -2974,17 +2974,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -8254,17 +8254,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>응답자키</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>respondent_key</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>P21-008155</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
@@ -8294,17 +8294,17 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -8766,17 +8766,17 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>응답자키</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>respondent_key</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>P21-008155</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
@@ -8806,17 +8806,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -9278,17 +9278,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>응답자키</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>respondent_key</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>원본 식별자를 치환한 대체키. 집계에 사용하지 않음. 주기 내에서만 유효하며 동일 주기의 학생·학부모는 같은 키로 연결됨. 주기가 다르면 서로 다른 사람</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>T21-004164</t>
+          <t>1001001</t>
         </is>
       </c>
     </row>
@@ -9318,17 +9318,17 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>학교키</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>school_key</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>원본 학교코드를 치환한 대체키. 주기 무관하게 동일 학교에 동일 키</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>SCH165</t>
+          <t>1001</t>
         </is>
       </c>
     </row>

--- a/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
+++ b/delivery/업체전달_데이터셋_v1/01_정의/테이블정의서.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -938,24 +938,24 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>학생 개인 단위 long</t>
+          <t>학생 개인 단위 long (1주기)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>03_마이크로데이터/micro_student.csv.gz</t>
+          <t>03_마이크로데이터/micro_student_2021.csv</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1391643</v>
+        <v>879516</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
@@ -967,57 +967,144 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>학부모 개인 단위 long</t>
+          <t>학생 개인 단위 long (2주기)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>03_마이크로데이터/micro_parent.csv.gz</t>
+          <t>03_마이크로데이터/micro_student_2025.csv</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>386360</v>
+        <v>512127</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>원자료</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>micro_teacher</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>교사 개인 단위 long</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>03_마이크로데이터/micro_teacher.csv.gz</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>620342</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>집계 재현 및 연도 갱신용</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent_2021</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>학부모 개인 단위 long (1주기)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>03_마이크로데이터/micro_parent_2021.csv</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>309296</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>원자료</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>micro_parent_2025</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>학부모 개인 단위 long (2주기)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>03_마이크로데이터/micro_parent_2025.csv</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>77064</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>원자료</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2021</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>교사 개인 단위 long (1주기)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>03_마이크로데이터/micro_teacher_2021.csv</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>404742</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>원자료</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>교사 개인 단위 long (2주기)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>03_마이크로데이터/micro_teacher_2025.csv</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>215600</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>집계 재현 및 연도 갱신용. 응답주체·주기별로 6개 파일</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2666,17 +2753,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>주기코드</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>wave_code</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2684,10 +2771,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -2702,17 +2793,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>주기번호</t>
+          <t>주기코드</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>wave_no</t>
+          <t>wave_code</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2723,7 +2814,7 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>W1</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2829,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>주기번호</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>wave_no</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2756,14 +2847,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2901,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2834,37 +2921,37 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>dim_region</t>
+          <t>dim_wave</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2874,12 +2961,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -2890,21 +2977,21 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2914,37 +3001,37 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>dim_school</t>
+          <t>dim_region</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2954,12 +3041,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
@@ -2970,16 +3057,16 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2994,12 +3081,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -3010,16 +3097,16 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3034,12 +3121,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -3050,16 +3137,16 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>설립구분코드</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>found_code</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3072,7 +3159,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -3086,16 +3177,16 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>남녀공학코드</t>
+          <t>설립구분코드</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>coed_code</t>
+          <t>found_code</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3111,7 +3202,7 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -3122,21 +3213,21 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>남녀공학코드</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>coed_code</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3144,14 +3235,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -3162,16 +3249,16 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>설립구분</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>found_name</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3184,10 +3271,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>공립</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
@@ -3198,16 +3289,16 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>남녀공학</t>
+          <t>설립구분</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>coed_name</t>
+          <t>found_name</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3223,7 +3314,7 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>남여공학</t>
+          <t>공립</t>
         </is>
       </c>
     </row>
@@ -3234,16 +3325,16 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>학생응답</t>
+          <t>남녀공학</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>has_student</t>
+          <t>coed_name</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3256,14 +3347,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>해당 주기에 이 학교에서 학생 응답이 수집되었는지 (Y/N)</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>남여공학</t>
         </is>
       </c>
     </row>
@@ -3274,16 +3361,16 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>학부모응답</t>
+          <t>학생응답</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>has_parent</t>
+          <t>has_student</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3298,7 +3385,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>해당 주기에 이 학교에서 학부모 응답이 수집되었는지 (Y/N)</t>
+          <t>해당 주기에 이 학교에서 학생 응답이 수집되었는지 (Y/N)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3314,16 +3401,16 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>교사응답</t>
+          <t>학부모응답</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>has_teacher</t>
+          <t>has_parent</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3338,7 +3425,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>해당 주기에 이 학교에서 교사 응답이 수집되었는지 (Y/N)</t>
+          <t>해당 주기에 이 학교에서 학부모 응답이 수집되었는지 (Y/N)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3350,20 +3437,20 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>dim_cross_respondent</t>
+          <t>dim_school</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>등급</t>
+          <t>교사응답</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>has_teacher</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3376,10 +3463,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>해당 주기에 이 학교에서 교사 응답이 수집되었는지 (Y/N)</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3390,16 +3481,16 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>성립여부</t>
+          <t>등급</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>is_valid</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3412,14 +3503,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>'성립'이면 다계열 그래프 구성 가능. '불가'는 한쪽 주체 문항이 미선택되어 단일 계열로 표시</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>성립</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3430,16 +3517,16 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>사유</t>
+          <t>성립여부</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>invalid_reason</t>
+          <t>is_valid</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3449,17 +3536,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>성립 불가 사유. 어느 주체가 미선택인지 표기</t>
+          <t>'성립'이면 다계열 그래프 구성 가능. '불가'는 한쪽 주체 문항이 미선택되어 단일 계열로 표시</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>깨짐(학부모 미선택)</t>
+          <t>성립</t>
         </is>
       </c>
     </row>
@@ -3470,16 +3557,16 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>비교조합</t>
+          <t>사유</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>pair</t>
+          <t>invalid_reason</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3489,13 +3576,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>성립 불가 사유. 어느 주체가 미선택인지 표기</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>학생–학부모</t>
+          <t>깨짐(학부모 미선택)</t>
         </is>
       </c>
     </row>
@@ -3506,16 +3597,16 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>주제</t>
+          <t>비교조합</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>topic</t>
+          <t>pair</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3531,7 +3622,7 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>전반적 학교만족도</t>
+          <t>학생–학부모</t>
         </is>
       </c>
     </row>
@@ -3542,14 +3633,18 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>학생_1주기</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>주제</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3563,7 +3658,7 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>전반적 학교만족도</t>
         </is>
       </c>
     </row>
@@ -3574,11 +3669,11 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>학생_2주기</t>
+          <t>학생_1주기</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -3595,7 +3690,7 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>STQ32</t>
+          <t>Q28</t>
         </is>
       </c>
     </row>
@@ -3606,11 +3701,11 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>학생판정</t>
+          <t>학생_2주기</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -3627,7 +3722,7 @@
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>STQ32</t>
         </is>
       </c>
     </row>
@@ -3638,11 +3733,11 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>학부모_1주기</t>
+          <t>학생판정</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -3659,7 +3754,7 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>① 연계가능</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3765,11 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>학부모_2주기</t>
+          <t>학부모_1주기</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -3691,7 +3786,7 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>PRQ14</t>
+          <t>Q15</t>
         </is>
       </c>
     </row>
@@ -3702,11 +3797,11 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>학부모판정</t>
+          <t>학부모_2주기</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -3723,7 +3818,7 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>① 연계가능</t>
+          <t>PRQ14</t>
         </is>
       </c>
     </row>
@@ -3734,11 +3829,11 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>교사_1주기</t>
+          <t>학부모판정</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -3755,7 +3850,7 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>① 연계가능</t>
         </is>
       </c>
     </row>
@@ -3766,11 +3861,11 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>교사_2주기</t>
+          <t>교사_1주기</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -3798,11 +3893,11 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>교사판정</t>
+          <t>교사_2주기</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -3830,18 +3925,14 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>척도</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>scale</t>
-        </is>
-      </c>
+          <t>교사판정</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
           <t>문자</t>
@@ -3855,7 +3946,7 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>5점 만족도</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3866,16 +3957,16 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>주의사항</t>
+          <t>척도</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3891,27 +3982,27 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>단일 문항이고 양 주기·양 주체 모두 불변. 대시보드 대표 지표로 가</t>
+          <t>5점 만족도</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave</t>
+          <t>dim_cross_respondent</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>주의사항</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>caution</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3924,14 +4015,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>단일 문항이고 양 주기·양 주체 모두 불변. 대시보드 대표 지표로 가</t>
         </is>
       </c>
     </row>
@@ -3942,16 +4029,16 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3966,12 +4053,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -3982,21 +4069,21 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4006,12 +4093,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -4022,21 +4109,21 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4046,12 +4133,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -4062,21 +4149,21 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4086,12 +4173,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
@@ -4102,21 +4189,21 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4126,12 +4213,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -4142,16 +4229,16 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4166,12 +4253,12 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
@@ -4182,16 +4269,16 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4206,12 +4293,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
@@ -4222,16 +4309,16 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4246,12 +4333,12 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
@@ -4262,16 +4349,16 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4286,12 +4373,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
@@ -4302,16 +4389,16 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4326,12 +4413,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
@@ -4342,16 +4429,16 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4366,12 +4453,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>ST_COMP_AC_CONV</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
@@ -4382,16 +4469,16 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4406,12 +4493,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>자율적 역량 환산점수(0~100)</t>
+          <t>ST_COMP_AC_CONV</t>
         </is>
       </c>
     </row>
@@ -4422,16 +4509,16 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>stat_type</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4446,12 +4533,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>자율적 역량 환산점수(0~100)</t>
         </is>
       </c>
     </row>
@@ -4462,16 +4549,16 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
+          <t>통계유형</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>comparable</t>
+          <t>stat_type</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4486,12 +4573,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>continuous</t>
         </is>
       </c>
     </row>
@@ -4502,36 +4589,36 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>대표값</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>headline_value</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>조건부</t>
         </is>
       </c>
     </row>
@@ -4542,21 +4629,21 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>대표값유형</t>
+          <t>대표값</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>headline_value_type</t>
+          <t>headline_value</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -4566,12 +4653,12 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
+          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>지출자 중앙값(만원)</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -4582,36 +4669,36 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>대표값유형</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>headline_value_type</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>지출자 중앙값(만원)</t>
         </is>
       </c>
     </row>
@@ -4622,16 +4709,16 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>결측수</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4646,12 +4733,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>결측 응답자 수</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8884</t>
         </is>
       </c>
     </row>
@@ -4662,21 +4749,21 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>평균</t>
+          <t>결측수</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>n_missing</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4686,12 +4773,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>원 척도 기준 평균</t>
+          <t>결측 응답자 수</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>70.2438</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4702,16 +4789,16 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>표준편차</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4726,12 +4813,12 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>표본표준편차</t>
+          <t>원 척도 기준 평균</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>13.5737</t>
+          <t>70.2438</t>
         </is>
       </c>
     </row>
@@ -4742,16 +4829,16 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>표준편차</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4766,12 +4853,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>표본표준편차</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>13.5737</t>
         </is>
       </c>
     </row>
@@ -4782,16 +4869,16 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>백분위25</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>median</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4804,10 +4891,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>중앙값</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -4818,16 +4909,16 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>백분위75</t>
+          <t>백분위25</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4843,7 +4934,7 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>79.16666666666666</t>
+          <t>62.5</t>
         </is>
       </c>
     </row>
@@ -4854,16 +4945,16 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>환산100</t>
+          <t>백분위75</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>scaled_100</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4873,17 +4964,13 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>79.16666666666666</t>
         </is>
       </c>
     </row>
@@ -4894,16 +4981,16 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>상위2선지비율</t>
+          <t>환산100</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>top2_pct</t>
+          <t>scaled_100</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -4918,12 +5005,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
+          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>21.82</t>
         </is>
       </c>
     </row>
@@ -4934,16 +5021,16 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>긍정응답률</t>
+          <t>상위2선지비율</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>top2_pct</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -4958,12 +5045,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>7.31</t>
         </is>
       </c>
     </row>
@@ -4974,16 +5061,16 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>절사평균</t>
+          <t>긍정응답률</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>trimmed_mean</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4996,10 +5083,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>70.6434</t>
+          <t>76.52</t>
         </is>
       </c>
     </row>
@@ -5010,21 +5101,21 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>지출자수</t>
+          <t>절사평균</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>n_payers</t>
+          <t>trimmed_mean</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5035,7 +5126,7 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>8884.0</t>
+          <t>70.6434</t>
         </is>
       </c>
     </row>
@@ -5046,21 +5137,21 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>지출참여율</t>
+          <t>지출자수</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>payer_pct</t>
+          <t>n_payers</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -5071,7 +5162,7 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>8884.0</t>
         </is>
       </c>
     </row>
@@ -5082,16 +5173,16 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>지출자평균</t>
+          <t>지출참여율</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>payer_mean</t>
+          <t>payer_pct</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5107,7 +5198,7 @@
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>70.2438</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -5118,16 +5209,16 @@
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>지출자중앙값</t>
+          <t>지출자평균</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>payer_median</t>
+          <t>payer_mean</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5140,54 +5231,50 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>70.2438</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>fact_topic_wave</t>
+          <t>fact_indicator_wave</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>지출자중앙값</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>payer_median</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -5198,16 +5285,16 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5222,12 +5309,12 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -5238,16 +5325,16 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5262,12 +5349,12 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -5278,16 +5365,16 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5302,12 +5389,12 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>학업</t>
+          <t>C02</t>
         </is>
       </c>
     </row>
@@ -5318,16 +5405,16 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5342,12 +5429,12 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>S0201A</t>
+          <t>학업</t>
         </is>
       </c>
     </row>
@@ -5358,16 +5445,16 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5382,12 +5469,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>학습동기(외재적)</t>
+          <t>S0201A</t>
         </is>
       </c>
     </row>
@@ -5398,16 +5485,16 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5422,12 +5509,12 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>학습동기(외재적)</t>
         </is>
       </c>
     </row>
@@ -5438,21 +5525,21 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5462,12 +5549,12 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
@@ -5478,21 +5565,21 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5502,12 +5589,12 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -5518,21 +5605,21 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>지표수</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>n_indicators</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -5540,10 +5627,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>'1주기' 또는 '2주기'</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
@@ -5554,21 +5645,21 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>평균환산100</t>
+          <t>지표수</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>mean_scaled_100</t>
+          <t>n_indicators</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -5579,7 +5670,7 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5590,21 +5681,21 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>평균응답수</t>
+          <t>평균환산100</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>mean_n_valid</t>
+          <t>mean_scaled_100</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -5615,32 +5706,32 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>5923.0</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>fact_headline</t>
+          <t>fact_topic_wave</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>평균응답수</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>mean_n_valid</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5648,14 +5739,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>5923.0</t>
         </is>
       </c>
     </row>
@@ -5666,16 +5753,16 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5690,12 +5777,12 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -5706,16 +5793,16 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -5730,12 +5817,12 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -5746,16 +5833,16 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -5770,12 +5857,12 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>진로·진학</t>
+          <t>C10</t>
         </is>
       </c>
     </row>
@@ -5786,16 +5873,16 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -5810,12 +5897,12 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>S1002</t>
+          <t>진로·진학</t>
         </is>
       </c>
     </row>
@@ -5826,16 +5913,16 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -5850,12 +5937,12 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>진로·진학 준비</t>
+          <t>S1002</t>
         </is>
       </c>
     </row>
@@ -5866,16 +5953,16 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -5890,12 +5977,12 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>진로·진학 준비</t>
         </is>
       </c>
     </row>
@@ -5906,21 +5993,21 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>값_2021</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>value_w1</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -5928,10 +6015,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>59.89</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
@@ -5942,16 +6033,16 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>값_2025</t>
+          <t>값_2021</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>value_w2</t>
+          <t>value_w1</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -5967,7 +6058,7 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>59.89</t>
         </is>
       </c>
     </row>
@@ -5978,21 +6069,21 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>직전시점</t>
+          <t>값_2025</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>prev_year</t>
+          <t>value_w2</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -6000,14 +6091,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>증감 계산의 기준이 된 이전 조사연도</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>72.09</t>
         </is>
       </c>
     </row>
@@ -6018,16 +6105,16 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>최신시점</t>
+          <t>직전시점</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>curr_year</t>
+          <t>prev_year</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6042,12 +6129,12 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>증감 계산의 기준이 된 최근 조사연도</t>
+          <t>증감 계산의 기준이 된 이전 조사연도</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -6058,21 +6145,21 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>증감</t>
+          <t>최신시점</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>curr_year</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -6080,10 +6167,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>증감 계산의 기준이 된 최근 조사연도</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -6094,16 +6185,16 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>증감률</t>
+          <t>증감</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>delta_pct</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6119,7 +6210,7 @@
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>12.2</t>
         </is>
       </c>
     </row>
@@ -6130,21 +6221,21 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>변화방향</t>
+          <t>증감률</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>delta_pct</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -6155,7 +6246,7 @@
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>증가</t>
+          <t>20.37</t>
         </is>
       </c>
     </row>
@@ -6166,21 +6257,21 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>절대증감순위</t>
+          <t>변화방향</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>abs_delta_rank</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6191,32 +6282,32 @@
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>증가</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_dist</t>
+          <t>fact_headline</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>절대증감순위</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>abs_delta_rank</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -6224,14 +6315,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6242,16 +6329,16 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6266,12 +6353,12 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -6282,16 +6369,16 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6306,12 +6393,12 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>PR_ASPIRE_01</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -6322,16 +6409,16 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6346,12 +6433,12 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>PR_ASPIRE_01</t>
         </is>
       </c>
     </row>
@@ -6362,16 +6449,16 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6386,12 +6473,12 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>진로·진학</t>
+          <t>C10</t>
         </is>
       </c>
     </row>
@@ -6402,16 +6489,16 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -6426,12 +6513,12 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>S1001</t>
+          <t>진로·진학</t>
         </is>
       </c>
     </row>
@@ -6442,16 +6529,16 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -6466,12 +6553,12 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>교육포부</t>
+          <t>S1001</t>
         </is>
       </c>
     </row>
@@ -6482,16 +6569,16 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6506,12 +6593,12 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>교육포부</t>
         </is>
       </c>
     </row>
@@ -6522,16 +6609,16 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6546,12 +6633,12 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>교육포부 - 교육포부</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
@@ -6562,21 +6649,21 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -6586,12 +6673,12 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>교육포부 - 교육포부</t>
         </is>
       </c>
     </row>
@@ -6602,21 +6689,21 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -6626,12 +6713,12 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -6642,21 +6729,21 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -6666,12 +6753,12 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>응답 선지 코드값</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
@@ -6682,16 +6769,16 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>code</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -6706,12 +6793,12 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>응답 선지 코드값</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -6722,21 +6809,21 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>비율</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>pct</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -6744,10 +6831,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -6758,52 +6849,52 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>선지라벨</t>
+          <t>비율</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>option_label</t>
+          <t>pct</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>고등학교 졸업</t>
+          <t>2.56</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>fact_indicator_wave_region</t>
+          <t>fact_indicator_dist</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>선지라벨</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>option_label</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -6813,17 +6904,13 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>고등학교 졸업</t>
         </is>
       </c>
     </row>
@@ -6834,16 +6921,16 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사명</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_name</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -6858,12 +6945,12 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>경기학교교육실태조사</t>
         </is>
       </c>
     </row>
@@ -6874,21 +6961,21 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>학교급</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>school_level</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -6898,12 +6985,12 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>중학교</t>
         </is>
       </c>
     </row>
@@ -6914,21 +7001,21 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -6938,12 +7025,12 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -6954,21 +7041,21 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>주기</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>wave_name</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -6978,12 +7065,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>'1주기' 또는 '2주기'</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1주기</t>
         </is>
       </c>
     </row>
@@ -6994,21 +7081,21 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -7018,12 +7105,12 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7034,16 +7121,16 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>대분류코드</t>
+          <t>지역규모</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>category_code</t>
+          <t>region_name</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7058,12 +7145,12 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>C01~C12. 화면 ② 대분류 탭</t>
+          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>중소도시</t>
         </is>
       </c>
     </row>
@@ -7074,16 +7161,16 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>대분류</t>
+          <t>대분류코드</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>category_name</t>
+          <t>category_code</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7098,12 +7185,12 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>대분류 표시명</t>
+          <t>C01~C12. 화면 ② 대분류 탭</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>학생성장</t>
+          <t>C01</t>
         </is>
       </c>
     </row>
@@ -7114,16 +7201,16 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>소주제코드</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>topic_code</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7138,12 +7225,12 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>S로 시작. 화면 ③ 소주제 탭</t>
+          <t>대분류 표시명</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>S0101</t>
+          <t>학생성장</t>
         </is>
       </c>
     </row>
@@ -7154,16 +7241,16 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>소주제</t>
+          <t>소주제코드</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>topic_name</t>
+          <t>topic_code</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7178,12 +7265,12 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>소주제 표시명</t>
+          <t>S로 시작. 화면 ③ 소주제 탭</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>역량점수</t>
+          <t>S0101</t>
         </is>
       </c>
     </row>
@@ -7194,16 +7281,16 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>소주제</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>topic_name</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7218,12 +7305,12 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>소주제 표시명</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>역량점수</t>
         </is>
       </c>
     </row>
@@ -7234,16 +7321,16 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -7258,12 +7345,12 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>ST_COMP_AC_CONV</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
@@ -7274,16 +7361,16 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>지표명</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7298,12 +7385,12 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>자율적 역량 환산점수(0~100)</t>
+          <t>ST_COMP_AC_CONV</t>
         </is>
       </c>
     </row>
@@ -7314,16 +7401,16 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>통계유형</t>
+          <t>지표명</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>stat_type</t>
+          <t>indicator_name</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7338,12 +7425,12 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
+          <t>화면 표시용 지표명 (문항명 - 하위문항)</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>자율적 역량 환산점수(0~100)</t>
         </is>
       </c>
     </row>
@@ -7354,16 +7441,16 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>시계열비교가능</t>
+          <t>통계유형</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>comparable</t>
+          <t>stat_type</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7378,12 +7465,12 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
+          <t>likert(선택형) / binary(이분형) / continuous(금액형) / excluded</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>조건부</t>
+          <t>continuous</t>
         </is>
       </c>
     </row>
@@ -7394,36 +7481,36 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>대표값</t>
+          <t>시계열비교가능</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>headline_value</t>
+          <t>comparable</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
+          <t>Y=그대로 비교 / 조건부=주의사항 확인 / N=시계열 제외</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>조건부</t>
         </is>
       </c>
     </row>
@@ -7434,21 +7521,21 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>대표값유형</t>
+          <t>대표값</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>headline_value_type</t>
+          <t>headline_value</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -7458,12 +7545,12 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
+          <t>★ 그래프 y축에 바로 사용. 지표 유형과 무관하게 채워짐</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>지출자 중앙값(만원)</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -7474,36 +7561,36 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>응답수</t>
+          <t>대표값유형</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>n_valid</t>
+          <t>headline_value_type</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>유효 응답자 수. 그래프에 병기 필요</t>
+          <t>★ 대표값의 단위·의미. 축 이름 표기에 사용</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>지출자 중앙값(만원)</t>
         </is>
       </c>
     </row>
@@ -7514,16 +7601,16 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>결측수</t>
+          <t>응답수</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>n_missing</t>
+          <t>n_valid</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -7538,12 +7625,12 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>결측 응답자 수</t>
+          <t>유효 응답자 수. 그래프에 병기 필요</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6985</t>
         </is>
       </c>
     </row>
@@ -7554,21 +7641,21 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>평균</t>
+          <t>결측수</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>n_missing</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -7578,12 +7665,12 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>원 척도 기준 평균</t>
+          <t>결측 응답자 수</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>70.3051</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7594,16 +7681,16 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>표준편차</t>
+          <t>평균</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -7618,12 +7705,12 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>표본표준편차</t>
+          <t>원 척도 기준 평균</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>13.536</t>
+          <t>70.3051</t>
         </is>
       </c>
     </row>
@@ -7634,16 +7721,16 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>표준편차</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -7658,12 +7745,12 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>중앙값</t>
+          <t>표본표준편차</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>13.536</t>
         </is>
       </c>
     </row>
@@ -7674,16 +7761,16 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>백분위25</t>
+          <t>중앙값</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>median</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -7696,10 +7783,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>중앙값</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
@@ -7710,16 +7801,16 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>백분위75</t>
+          <t>백분위25</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -7735,7 +7826,7 @@
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>79.16666666666666</t>
+          <t>62.5</t>
         </is>
       </c>
     </row>
@@ -7746,16 +7837,16 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>환산100</t>
+          <t>백분위75</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>scaled_100</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -7765,17 +7856,13 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>79.16666666666666</t>
         </is>
       </c>
     </row>
@@ -7786,16 +7873,16 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>상위2선지비율</t>
+          <t>환산100</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>top2_pct</t>
+          <t>scaled_100</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -7810,12 +7897,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
+          <t>(평균-척도최소)/(척도최대-척도최소)×100. 선택형 지표만</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>22.0</t>
         </is>
       </c>
     </row>
@@ -7826,16 +7913,16 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>긍정응답률</t>
+          <t>상위2선지비율</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>positive_pct</t>
+          <t>top2_pct</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -7850,12 +7937,12 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+          <t>최상위 2개 선지 응답 비율(%). 선택형 지표만</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>7.53</t>
         </is>
       </c>
     </row>
@@ -7866,16 +7953,16 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>절사평균</t>
+          <t>긍정응답률</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>trimmed_mean</t>
+          <t>positive_pct</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -7888,10 +7975,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>긍정코드 응답 비율(%). 이분형 지표만</t>
+        </is>
+      </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>70.6843</t>
+          <t>78.3</t>
         </is>
       </c>
     </row>
@@ -7902,21 +7993,21 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>지출자수</t>
+          <t>절사평균</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>n_payers</t>
+          <t>trimmed_mean</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -7927,7 +8018,7 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>6985.0</t>
+          <t>70.6843</t>
         </is>
       </c>
     </row>
@@ -7938,21 +8029,21 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>지출참여율</t>
+          <t>지출자수</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>payer_pct</t>
+          <t>n_payers</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -7963,7 +8054,7 @@
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>6985.0</t>
         </is>
       </c>
     </row>
@@ -7974,16 +8065,16 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>지출자평균</t>
+          <t>지출참여율</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>payer_mean</t>
+          <t>payer_pct</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -7999,7 +8090,7 @@
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>70.3051</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -8010,16 +8101,16 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>지출자중앙값</t>
+          <t>지출자평균</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>payer_median</t>
+          <t>payer_mean</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8032,79 +8123,75 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
-        </is>
-      </c>
+      <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>70.83333333333334</t>
+          <t>70.3051</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>fact_indicator_wave_region</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>지출자중앙값</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>payer_median</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>0 초과 응답자의 중앙값. 금액형 지표만</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>70.83333333333334</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -8114,37 +8201,37 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -8154,37 +8241,37 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>학생</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -8194,37 +8281,37 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -8234,37 +8321,37 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>학생</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>응답자ID</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>respondent_id</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -8274,72 +8361,72 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>10011001</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>값</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>응답값 (코드 또는 실수)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>결측보정</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>missing_fix</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -8349,42 +8436,42 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>ST_PRIVED_TYPE_01</t>
+          <t>기저정렬(Q10=1)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2021</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>원변수명</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>source_var</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -8392,30 +8479,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Q10_1_1</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -8430,68 +8521,72 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>응답값 (코드 또는 실수)</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>결측보정</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>missing_fix</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr"/>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>학생</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>지역규모코드</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>region_code</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -8506,37 +8601,37 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>micro_student</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -8546,32 +8641,32 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -8586,117 +8681,113 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>ST_PRIVED_TYPE_01</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>값</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>응답값 (코드 또는 실수)</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>결측보정</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>missing_fix</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_student_2025</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -8706,37 +8797,37 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -8746,37 +8837,37 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>학부모</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>응답자ID</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>respondent_id</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -8786,32 +8877,32 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>10011001</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -8826,37 +8917,37 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>10011001</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -8866,32 +8957,32 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>PR_EDU_COST_01</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>원변수명</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>source_var</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -8904,21 +8995,25 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>Q3_1</t>
+          <t>PR_EDU_COST_01</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
@@ -8937,7 +9032,7 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -8954,11 +9049,11 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
@@ -8972,7 +9067,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>문자</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -8985,16 +9080,20 @@
           <t>적용된 보정 내용. 공란이면 원값 그대로</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>미선택→0</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2021</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
@@ -9030,25 +9129,25 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>micro_parent</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>지역규모</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>region_name</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -9058,32 +9157,32 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>중소도시</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>조사명</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>survey_name</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -9098,37 +9197,37 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>고정값 '경기학교교육실태조사'. 향후 타 조사 확장 대비</t>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>경기학교교육실태조사</t>
+          <t>학부모</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>학교급</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>school_level</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -9138,32 +9237,32 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>고정값 '중학교'. 초·고 확장 시 값이 늘어남 (화면 ① 전역 필터)</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>중학교</t>
+          <t>10011006</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>조사연도</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>survey_year</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -9178,32 +9277,32 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>2021(1주기) 또는 2025(2주기)</t>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>주기</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>wave_name</t>
+          <t>indicator_id</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -9218,112 +9317,108 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>'1주기' 또는 '2주기'</t>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>1주기</t>
+          <t>PR_EDU_COST_01</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>응답주체</t>
+          <t>값</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>respondent</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+          <t>응답값 (코드 또는 실수)</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>교사</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>응답자ID</t>
+          <t>결측보정</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>respondent_id</t>
+          <t>missing_fix</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>정수</t>
+          <t>실수</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>1001001</t>
-        </is>
-      </c>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_parent_2025</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>학교ID</t>
+          <t>지역규모코드</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>region_code</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -9338,37 +9433,37 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>조사연도</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>survey_year</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>문자</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -9378,32 +9473,32 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+          <t>2021(1주기) 또는 2025(2주기)</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>TR_EFFICACY_01</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>원변수명</t>
+          <t>응답주체</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>source_var</t>
+          <t>respondent</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -9416,30 +9511,34 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>Q9_1</t>
+          <t>교사</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>응답자ID</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -9454,128 +9553,524 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>응답값 (코드 또는 실수)</t>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>1001001</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>결측보정</t>
+          <t>학교ID</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>missing_fix</t>
+          <t>school_id</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>실수</t>
+          <t>정수</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="inlineStr"/>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>micro_teacher</t>
+          <t>micro_teacher_2021</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>TR_EFFICACY_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2021</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>응답값 (코드 또는 실수)</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2021</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>결측보정</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>missing_fix</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>실수</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2021</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
           <t>지역규모코드</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>region_code</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>정수</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>0=전체, 1=중소도시, 2=읍면지역</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>micro_teacher</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>지역규모</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>region_name</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>문자</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>'전체' / '중소도시' / '읍면지역'. ⑤-① 추이는 '전체', ⑤-② 비교는 '전체' 제외</t>
-        </is>
-      </c>
-      <c r="H221" s="3" t="inlineStr">
-        <is>
-          <t>중소도시</t>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>조사연도</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>survey_year</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>2021(1주기) 또는 2025(2주기)</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>응답주체</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>respondent</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>'학생' / '학부모' / '교사'. 다계열 그래프의 계열 구분</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>교사</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>응답자ID</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>respondent_id</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>학생·학부모는 STUID(학부모는 자녀의 학생 ID), 교사는 TID. 집계에는 사용하지 않는다. 동일 주기의 학생·학부모는 같은 값으로 연결되나, 주기가 다르면 서로 다른 사람이다</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>10011491</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>학교ID</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>school_id</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>SCHID. 주기 간 동일 학교를 가리킴</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>indicator_id</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>문자</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>지표 고유 식별자. 주기가 바뀌어도 불변 (전 테이블 조인 키)</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>TR_EFFICACY_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>응답값 (코드 또는 실수)</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>결측보정</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>missing_fix</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>실수</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>적용된 보정 내용. 공란이면 원값 그대로</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>micro_teacher_2025</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>지역규모코드</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>region_code</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>정수</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>0=전체, 1=중소도시, 2=읍면지역</t>
+        </is>
+      </c>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
